--- a/tests/fixtures/rich/showcase.xlsx
+++ b/tests/fixtures/rich/showcase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rutba2.0\office\tests\fixtures\rich\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{415794CF-4092-4DA5-982C-304D1468047A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF14EC3F-FBDD-404D-A746-DCC1A5E9F7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EA27F8CD-C773-4BA2-878C-E0FEC4362FFA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B32332A6-EAFE-4225-9984-CAFE88A9815A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
     <author>Ejaz Arain</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{1A131A49-63DF-4A6E-96C0-ECBBA0AB54DD}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{839680DB-ABD1-4DB6-A51E-34C634AE5E1D}">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Months of the year 2026-09-10 00:51 - a plain note, not a threaded comment.</t>
+          <t>Months of the year 2026-09-10 01:45 - a plain note, not a threaded comment.</t>
         </r>
       </text>
     </comment>
@@ -956,7 +956,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E5B1-4A06-AEAD-72447C07928F}"/>
+              <c16:uniqueId val="{00000000-F4E0-4892-AFF7-C5E64C3CAA2C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1245,7 +1245,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9004-4028-A607-FE23741CB478}"/>
+              <c16:uniqueId val="{00000000-4482-4FC7-9869-44A1ADE6ED3E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1364,7 +1364,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9004-4028-A607-FE23741CB478}"/>
+              <c16:uniqueId val="{00000001-4482-4FC7-9869-44A1ADE6ED3E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1483,7 +1483,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-9004-4028-A607-FE23741CB478}"/>
+              <c16:uniqueId val="{00000002-4482-4FC7-9869-44A1ADE6ED3E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1602,7 +1602,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-9004-4028-A607-FE23741CB478}"/>
+              <c16:uniqueId val="{00000003-4482-4FC7-9869-44A1ADE6ED3E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1616,11 +1616,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="527432111"/>
-        <c:axId val="403170831"/>
+        <c:axId val="499085871"/>
+        <c:axId val="470554607"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="527432111"/>
+        <c:axId val="499085871"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1663,7 +1663,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403170831"/>
+        <c:crossAx val="470554607"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1671,7 +1671,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="403170831"/>
+        <c:axId val="470554607"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1722,7 +1722,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527432111"/>
+        <c:crossAx val="499085871"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1971,7 +1971,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-318D-42F3-8BB5-19883CEFCC43}"/>
+              <c16:uniqueId val="{00000000-4DD9-4182-A42B-CC18C7EA7410}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2093,7 +2093,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-318D-42F3-8BB5-19883CEFCC43}"/>
+              <c16:uniqueId val="{00000001-4DD9-4182-A42B-CC18C7EA7410}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2215,7 +2215,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-318D-42F3-8BB5-19883CEFCC43}"/>
+              <c16:uniqueId val="{00000002-4DD9-4182-A42B-CC18C7EA7410}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2337,7 +2337,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-318D-42F3-8BB5-19883CEFCC43}"/>
+              <c16:uniqueId val="{00000003-4DD9-4182-A42B-CC18C7EA7410}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2350,11 +2350,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="532229839"/>
-        <c:axId val="403167471"/>
+        <c:axId val="499090975"/>
+        <c:axId val="470550767"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="532229839"/>
+        <c:axId val="499090975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2397,7 +2397,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403167471"/>
+        <c:crossAx val="470550767"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2405,7 +2405,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="403167471"/>
+        <c:axId val="470550767"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2456,7 +2456,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532229839"/>
+        <c:crossAx val="499090975"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2746,7 +2746,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-466B-4501-9EFD-FC402A2EE7F6}"/>
+              <c16:uniqueId val="{00000000-F04D-4D09-B5BB-414E799B4070}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2759,11 +2759,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="532226127"/>
-        <c:axId val="403168431"/>
+        <c:axId val="499098399"/>
+        <c:axId val="470552687"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="532226127"/>
+        <c:axId val="499098399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2806,7 +2806,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403168431"/>
+        <c:crossAx val="470552687"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2814,7 +2814,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="403168431"/>
+        <c:axId val="470552687"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2865,7 +2865,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532226127"/>
+        <c:crossAx val="499098399"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3110,7 +3110,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7DDF-48EA-81AB-F875120AE27D}"/>
+              <c16:uniqueId val="{00000000-BD8D-4E3C-BCBF-023A95CA9524}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3228,7 +3228,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7DDF-48EA-81AB-F875120AE27D}"/>
+              <c16:uniqueId val="{00000001-BD8D-4E3C-BCBF-023A95CA9524}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3346,7 +3346,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7DDF-48EA-81AB-F875120AE27D}"/>
+              <c16:uniqueId val="{00000002-BD8D-4E3C-BCBF-023A95CA9524}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3464,7 +3464,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7DDF-48EA-81AB-F875120AE27D}"/>
+              <c16:uniqueId val="{00000003-BD8D-4E3C-BCBF-023A95CA9524}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3476,11 +3476,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="414795279"/>
-        <c:axId val="403158351"/>
+        <c:axId val="499100719"/>
+        <c:axId val="470543567"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="414795279"/>
+        <c:axId val="499100719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3523,7 +3523,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403158351"/>
+        <c:crossAx val="470543567"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3531,7 +3531,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="403158351"/>
+        <c:axId val="470543567"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3582,7 +3582,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="414795279"/>
+        <c:crossAx val="499100719"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6422,7 +6422,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A67F7A6E-4EC3-EA39-563C-2DCFFB8DB5CD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BF8375C-22F7-B739-EC30-7E82C80C5806}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6463,7 +6463,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D7BC7CC-6CFE-0701-56A9-8E7123951465}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F58C8F38-0FBD-11A6-2F80-234CE567E7AD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6499,7 +6499,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE764A3B-F138-E258-7A02-086DF293E294}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1B20EC9-77D2-A1EA-FDE0-8D97D581DCA3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6535,7 +6535,7 @@
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E857D220-5F0D-9534-0931-7F28F6AC8CEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FB07255-A3EF-9988-C1AC-2DBF4AD1A65B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6571,7 +6571,7 @@
         <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3380C722-A6F5-F54C-1543-827749AB2ABB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40FDB498-DB30-1015-E245-95E8318BA606}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6607,7 +6607,7 @@
         <xdr:cNvPr id="6" name="Shape Rectangle">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F12FA55-D8E7-8E97-1188-00C17E4FF392}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4213FA3-1F31-6E1E-E690-3F65482FE187}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6682,7 +6682,7 @@
         <xdr:cNvPr id="7" name="Shape Rounded">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D4247FE-BA6E-DEF9-C329-ED9B25177755}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3880594A-CBAC-A78A-D292-74FC9FB740C9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6766,7 +6766,7 @@
         <xdr:cNvPr id="8" name="Shape Oval">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2CBBCF-9A7B-D1EB-1207-649D450DB24D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C07A2DD5-4833-10FB-9A9A-5B851F8EF487}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6841,7 +6841,7 @@
         <xdr:cNvPr id="9" name="Shape Triangle">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A64CB176-5F8B-85E4-C121-21E7E856BE36}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DCEC3A7-810D-2550-23E3-705D2958D3D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6921,7 +6921,7 @@
         <xdr:cNvPr id="10" name="Shape Star">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89D4B2C1-6415-9ADA-5AA4-5FB91FB205C0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{407F3A8C-9352-6A4C-CF1E-FD73DD304824}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7005,7 +7005,7 @@
         <xdr:cNvPr id="11" name="Shape Arrow">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4767686E-EA9D-1936-8824-4D042BFF4E96}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{415E4135-6CD6-6979-E1E4-AA82794AE4F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7080,7 +7080,7 @@
         <xdr:cNvPr id="12" name="Shape Chevron">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D33DE97C-F73C-1174-0E4F-841AEEE20EFA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C788B3A-0787-32A9-372A-6D0ED7E0A9B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7155,7 +7155,7 @@
         <xdr:cNvPr id="13" name="Shape Hexagon">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6387AB7-7854-6944-3261-8D831050282F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF1B54B8-4953-80D2-2FC0-440DE72D94F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7244,7 +7244,7 @@
         <xdr:cNvPr id="14" name="Shape Heart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{365CD6EA-933C-4B8B-BD38-7682B48C6C10}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3BB29AA-B5B1-480B-75D8-0F6A1FC46A1B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7319,7 +7319,7 @@
         <xdr:cNvPr id="15" name="Shape Smile">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCCBF756-0110-C1F3-3CA9-CA5E64E97424}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E295D737-606D-35C6-2218-2E29686E7F66}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7394,7 +7394,7 @@
         <xdr:cNvPr id="16" name="Shape Process">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63B9683E-A127-37E0-4D30-6802BECDBAE1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E7614A1-A26D-A8F7-0913-C8133BDDE36C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7478,7 +7478,7 @@
         <xdr:cNvPr id="17" name="Shape Callout">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41123958-2E56-5A9E-B316-AD2684248781}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C267F29C-E5B5-B8DA-3E63-7A6ED30CB357}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7558,7 +7558,7 @@
         <xdr:cNvPr id="19" name="Picture 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF778A4-5815-7E01-D9BF-029D8289DBEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80E761AA-D695-F632-EA61-77B6A7AC83B1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7608,7 +7608,7 @@
         <xdr:cNvPr id="20" name="TextBox 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD9876FE-00A5-7440-516F-292044A09F38}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C1CCB82-D84B-91F5-DE00-CF6DD280788D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7692,7 +7692,7 @@
         <xdr:cNvPr id="23" name="Two circles">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBCAE3EC-5B1E-5644-95F7-33C459B1047E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{932C5D9A-7E5E-5E4F-94CF-1BA5CE34D847}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7711,7 +7711,7 @@
           <xdr:cNvPr id="21" name="GroupA">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C9DAE6D-5BDC-481F-3F0B-CD1232B25FEF}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A35957F4-EB9E-1E49-A086-5F2D55DE8926}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7759,7 +7759,7 @@
           <xdr:cNvPr id="22" name="GroupB">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F202DAA-17F6-45EC-0B52-6757C2167950}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C17D404B-E980-879E-AC75-D6890CA44766}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7823,7 +7823,7 @@
         <xdr:cNvPr id="24" name="Rectangle 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EA6E7AB-21E2-23F0-9CE8-CD814DBADC23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86B9A6A8-E288-07EB-5021-28BAB2865C0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7889,7 +7889,7 @@
         <xdr:cNvPr id="25" name="Connector: Elbow 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28BAA2B8-CD44-C2F3-9251-B5D5B755A138}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E972999-389C-E4C9-3F9C-67198CBAFF7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7925,13 +7925,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CA860045-3AF5-4921-99B3-6C67DBE34A39}" name="Orders" displayName="Orders" ref="A1:D8" totalsRowCount="1">
-  <autoFilter ref="A1:D7" xr:uid="{CA860045-3AF5-4921-99B3-6C67DBE34A39}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BB0EBC31-8076-437B-8D10-142DA7CAD925}" name="Orders" displayName="Orders" ref="A1:D8" totalsRowCount="1">
+  <autoFilter ref="A1:D7" xr:uid="{BB0EBC31-8076-437B-8D10-142DA7CAD925}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C9064E8E-1B0C-46FC-9BE4-5CEAED10BC69}" name="Product" totalsRowLabel="Total"/>
-    <tableColumn id="2" xr3:uid="{F498CE18-A934-4AB8-B7D8-B4F9474EDF68}" name="Quantity"/>
-    <tableColumn id="3" xr3:uid="{F4BE2F9E-7A4E-420A-8721-9613340320C1}" name="Price" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{7EE65220-784F-489E-BEF4-1D6C8325D7CE}" name="Amount" totalsRowFunction="sum" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{E74ABB1D-693C-4614-ACF7-5033695390AB}" name="Product" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{A72D07AC-916F-409F-B0EB-06C00AD6BE83}" name="Quantity"/>
+    <tableColumn id="3" xr3:uid="{7B7FEC4C-048D-497C-B7A6-45CEF7D93C72}" name="Price" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{89F2806E-0B2A-4A9F-B304-4DFE9B694288}" name="Amount" totalsRowFunction="sum" dataDxfId="0">
       <calculatedColumnFormula>B2*C2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8255,7 +8255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDEAB76-3F0F-430F-9452-1FC4463CF2BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BD3880-9E53-4CB2-A790-6D78A59019D2}">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8720,7 +8720,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13" xr:uid="{5EDEAB76-3F0F-430F-9452-1FC4463CF2BF}"/>
+  <autoFilter ref="A1:H13" xr:uid="{F5BD3880-9E53-4CB2-A790-6D78A59019D2}"/>
   <conditionalFormatting sqref="B2:E13">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -8742,7 +8742,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9E74881A-9165-415D-BF28-B7FBF912DDEE}</x14:id>
+          <x14:id>{5221ADD7-2263-4A7C-B848-81E40BC9180A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8757,12 +8757,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21" xr:uid="{E268854A-7F04-406D-9DB5-106C5FE0366B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21" xr:uid="{1466060E-0EF8-4420-A5F3-4B7207CEA754}">
       <formula1>"Yes,No,Maybe"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A19" r:id="rId1" tooltip="The free suite" xr:uid="{01307902-DD1F-41F1-BC79-09CC1D4E9EC9}"/>
+    <hyperlink ref="A19" r:id="rId1" tooltip="The free suite" xr:uid="{B3D97404-9C15-49D4-A42F-4901ABE6E7C2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
@@ -8770,7 +8770,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9E74881A-9165-415D-BF28-B7FBF912DDEE}">
+          <x14:cfRule type="dataBar" id="{5221ADD7-2263-4A7C-B848-81E40BC9180A}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8782,7 +8782,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{E87E98F7-B80B-4C31-BE88-FE32E3C95D88}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{212AC098-6740-4043-8F04-09385C8FE6FC}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -8849,7 +8849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE7A8FD5-64DD-4EA9-B67C-C8D0FF7B9713}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B44C319D-76C7-4948-BCF1-3CFBBE077563}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9042,7 +9042,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8901608D-905D-4A9A-8AA1-BC31D22F7FE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040E77CD-A053-42DF-8E17-1DB101C09F08}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -9052,7 +9052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F07354-BC68-42EE-AC37-195F2F3BCB8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4444920C-1B41-455F-8C97-E51F7E15C42C}">
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9347,7 +9347,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B95F25D-D0B2-4537-8D52-65DD66A26673}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECDD157-DB68-424D-8050-B609BE1C2B36}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
